--- a/pipeline/cohorts/HKIPO-MB2025Q4.xlsx
+++ b/pipeline/cohorts/HKIPO-MB2025Q4.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17400" tabRatio="654" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NLR" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="NLR" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'NLR'!$1:$1</definedName>
@@ -26304,8 +26304,10 @@
           <t>NaN</t>
         </is>
       </c>
-      <c r="BH39" s="161" t="n">
-        <v>1</v>
+      <c r="BH39" s="161" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
       </c>
       <c r="BI39" s="161" t="inlineStr">
         <is>
